--- a/artfynd/A 46204-2023 artfynd.xlsx
+++ b/artfynd/A 46204-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46204-2023 artfynd.xlsx
+++ b/artfynd/A 46204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99324786</v>
+        <v>117785348</v>
       </c>
       <c r="B2" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FM-1721-5-25, Upl</t>
+          <t>Forsmark, 1 km V kraftverket, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673276.1964830536</v>
+        <v>673030</v>
       </c>
       <c r="R2" t="n">
-        <v>6700797.932259362</v>
+        <v>6700805</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,25 +750,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-05-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-05-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,54 +766,46 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
+          <t>Rikard Anderberg, Maya Edlund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99367988</v>
+        <v>99326081</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,14 +820,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FM-44-2-92, Upl</t>
+          <t>FM-19045-5-48, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673248.4407195983</v>
+        <v>673283</v>
       </c>
       <c r="R3" t="n">
-        <v>6700704.565031807</v>
+        <v>6700721</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,22 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-05-22</t>
+          <t>2013-05-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-05-22</t>
+          <t>2013-05-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:56</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99367985</v>
+        <v>99341019</v>
       </c>
       <c r="B4" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,16 +911,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>102963</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,19 +930,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>FM-44-2-92, Upl</t>
+          <t>FM-233-5-24, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673248.4407195983</v>
+        <v>673275</v>
       </c>
       <c r="R4" t="n">
-        <v>6700704.565031807</v>
+        <v>6700665</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,9 +967,10 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-05-20</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1000,7 +980,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-05-20</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1029,6 +1009,929 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99366138</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58212</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FM-670-3-27, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>673287</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6700818</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2002-06-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2002-06-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>99357476</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FM-3761-1-21, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>673271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6700772</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>99341016</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FM-233-5-24, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>673275</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6700665</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-06-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99367985</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FM-44-2-92, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>673248</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6700704</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99324786</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FM-1721-5-25, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>673276</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6700798</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2003-05-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2003-05-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99357474</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FM-3761-1-21, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>673271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6700772</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99357477</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FM-3761-1-21, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>673271</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6700772</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2007-06-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>99367988</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FM-44-2-92, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>673248</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6700704</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-05-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-05-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Forsmark platsundersökning</t>
         </is>

--- a/artfynd/A 46204-2023 artfynd.xlsx
+++ b/artfynd/A 46204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117785348</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99326081</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99341019</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99366138</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99357476</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99341016</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367985</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1591,6 +1631,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99324786</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99357474</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99357477</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,8 +1991,26 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367988</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>